--- a/outputs/03_audit_metal_support/Combined_support_audit.xlsx
+++ b/outputs/03_audit_metal_support/Combined_support_audit.xlsx
@@ -7814,19 +7814,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H2">
         <v>3</v>
@@ -7844,10 +7844,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -7856,7 +7856,7 @@
         <v>2</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H3">
         <v>0</v>
